--- a/JsonConverter/ExcelFiles/WJUnit.xlsx
+++ b/JsonConverter/ExcelFiles/WJUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B54777-A0B9-4676-9499-2AB7FFE46EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4151DBE7-BC95-4961-974A-B3724DD39C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="2415" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4020" yWindow="1680" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Unit" sheetId="1" r:id="rId1"/>
@@ -82,10 +82,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>5f</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Unit_Enemy_1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -98,15 +94,19 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>1f</t>
+    <t>2.5</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>2.5f</t>
+    <t>0.0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>0f</t>
+    <t>5.0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -245,6 +245,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -542,14 +548,14 @@
       <c r="D4" s="4">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>15</v>
+      <c r="E4" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>21</v>
+      <c r="G4" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -562,25 +568,25 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="D5" s="5">
         <v>5</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>19</v>
+      <c r="E5" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F5" s="5">
         <v>5</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>20</v>
+      <c r="G5" s="13" t="s">
+        <v>18</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>

--- a/JsonConverter/ExcelFiles/WJUnit.xlsx
+++ b/JsonConverter/ExcelFiles/WJUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4151DBE7-BC95-4961-974A-B3724DD39C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323C5CEB-E02E-4EBF-8055-289723F6A31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="1680" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32850" yWindow="4110" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Unit" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>(name)</t>
   </si>
@@ -107,6 +107,22 @@
   </si>
   <si>
     <t>1.0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>_path</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/WJ2DPlayer</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/2D/Enemy</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -475,7 +491,7 @@
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="7" max="8" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -488,6 +504,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -511,6 +528,9 @@
       <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -534,6 +554,9 @@
       <c r="G3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -557,7 +580,9 @@
       <c r="G4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -588,7 +613,9 @@
       <c r="G5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -605,7 +632,7 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -622,7 +649,7 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -639,7 +666,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="6"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -656,7 +683,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="6"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -673,7 +700,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="7"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -690,7 +717,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -707,7 +734,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -724,7 +751,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="4"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -741,7 +768,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="7"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -758,7 +785,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -775,8 +802,9 @@
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -784,8 +812,9 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -793,8 +822,9 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -802,8 +832,9 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -811,8 +842,9 @@
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -820,8 +852,9 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -829,8 +862,9 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -838,8 +872,9 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H23" s="9"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -847,8 +882,9 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -856,8 +892,9 @@
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -865,8 +902,9 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -874,8 +912,9 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -883,8 +922,9 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -892,8 +932,9 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -901,8 +942,9 @@
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -910,8 +952,9 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -919,8 +962,9 @@
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H32" s="11"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -928,8 +972,9 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H33" s="11"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -937,8 +982,9 @@
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1">
+      <c r="H34" s="11"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -946,20 +992,21 @@
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1"/>
+      <c r="H35" s="11"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WJUnit.xlsx
+++ b/JsonConverter/ExcelFiles/WJUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323C5CEB-E02E-4EBF-8055-289723F6A31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6437D641-61CB-46CA-B8CE-ECCFE837FCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32850" yWindow="4110" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="585" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Unit" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>(name)</t>
   </si>
@@ -94,10 +94,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>2.5</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>0.0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -114,15 +110,55 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>_path</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/2D/WJ2DPlayer</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Prefabs/2D/Enemy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>_prefabPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>_spritePath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>_animePath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D/WJ_Folder/Enemies/bat/bat-fly/Enemy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D/WJ_Folder/Enemies/bat/bat-fly/bat-fly1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unit_Enemy_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D/WJ_Folder/Enemies/bear/bear-walk1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -491,7 +527,7 @@
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="8" width="18.28515625" customWidth="1"/>
+    <col min="7" max="10" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -505,6 +541,8 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -529,7 +567,13 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
@@ -555,7 +599,13 @@
         <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -572,19 +622,19 @@
         <v>10</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -605,19 +655,23 @@
         <v>5</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F5" s="5">
         <v>5</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -625,16 +679,36 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="A6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5">
+        <v>100</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5">
+        <v>50</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -650,8 +724,8 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -667,8 +741,8 @@
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -684,8 +758,8 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -701,8 +775,8 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -718,8 +792,8 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -735,8 +809,8 @@
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -752,8 +826,8 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -769,8 +843,8 @@
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -786,8 +860,8 @@
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -803,8 +877,10 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -813,8 +889,10 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -823,8 +901,10 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -833,8 +913,10 @@
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -843,8 +925,10 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -853,8 +937,10 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -863,8 +949,10 @@
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -873,8 +961,10 @@
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -883,8 +973,10 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -893,8 +985,10 @@
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -903,8 +997,10 @@
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -913,8 +1009,10 @@
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -923,8 +1021,10 @@
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -933,8 +1033,10 @@
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -943,8 +1045,10 @@
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -953,8 +1057,10 @@
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -963,8 +1069,10 @@
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -973,8 +1081,10 @@
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -983,8 +1093,10 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -993,20 +1105,22 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:10" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WJUnit.xlsx
+++ b/JsonConverter/ExcelFiles/WJUnit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6437D641-61CB-46CA-B8CE-ECCFE837FCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB20FFA2-F3F6-4BE1-9655-FFBB144711EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="585" windowWidth="21270" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29385" yWindow="3225" windowWidth="20370" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Unit" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>(name)</t>
   </si>
@@ -159,6 +159,22 @@
   </si>
   <si>
     <t>2D/WJ_Folder/Enemies/bear/bear-walk1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>_exp</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>100</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -521,16 +537,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:P1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="10" width="18.28515625" customWidth="1"/>
+    <col min="7" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -543,8 +559,9 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -567,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>21</v>
@@ -575,8 +592,11 @@
       <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1">
+      <c r="K2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -599,16 +619,19 @@
         <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+    <row r="4" spans="1:16" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -631,17 +654,20 @@
         <v>18</v>
       </c>
       <c r="H4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="12"/>
       <c r="J4" s="12"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="12"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="1:16" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -664,21 +690,24 @@
         <v>20</v>
       </c>
       <c r="H5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="J5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="K5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>29</v>
       </c>
@@ -701,21 +730,24 @@
         <v>33</v>
       </c>
       <c r="H6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="13" t="s">
         <v>23</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>34</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P6" s="3"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -726,13 +758,14 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="4"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" spans="1:16" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -743,13 +776,14 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -760,13 +794,14 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="6"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" ht="15.75" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -777,13 +812,14 @@
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="7"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -794,13 +830,14 @@
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="7"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -811,13 +848,14 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="6"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -828,13 +866,14 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="3"/>
+      <c r="K13" s="4"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -845,13 +884,14 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="7"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -862,13 +902,14 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="7"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -879,8 +920,9 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" ht="15.75" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -891,8 +933,9 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K17" s="9"/>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -903,8 +946,9 @@
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K18" s="9"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -915,8 +959,9 @@
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="1:11" ht="15.75" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -927,8 +972,9 @@
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K20" s="9"/>
+    </row>
+    <row r="21" spans="1:11" ht="15.75" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -939,8 +985,9 @@
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" spans="1:11" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -951,8 +998,9 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -963,8 +1011,9 @@
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -975,8 +1024,9 @@
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K24" s="9"/>
+    </row>
+    <row r="25" spans="1:11" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -987,8 +1037,9 @@
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
-    </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K25" s="9"/>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -999,8 +1050,9 @@
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K26" s="10"/>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -1011,8 +1063,9 @@
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -1023,8 +1076,9 @@
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
-    </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K28" s="10"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -1035,8 +1089,9 @@
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
       <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -1047,8 +1102,9 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
       <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K30" s="10"/>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -1059,8 +1115,9 @@
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
       <c r="J31" s="10"/>
-    </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K31" s="10"/>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1071,8 +1128,9 @@
       <c r="H32" s="11"/>
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" spans="1:11" ht="15.75" customHeight="1">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1083,8 +1141,9 @@
       <c r="H33" s="11"/>
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
-    </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" customHeight="1">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1095,8 +1154,9 @@
       <c r="H34" s="11"/>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1">
+      <c r="K34" s="11"/>
+    </row>
+    <row r="35" spans="1:11" ht="15.75" customHeight="1">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1107,20 +1167,21 @@
       <c r="H35" s="11"/>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
-    </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1"/>
+      <c r="K35" s="11"/>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/WJUnit.xlsx
+++ b/JsonConverter/ExcelFiles/WJUnit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB20FFA2-F3F6-4BE1-9655-FFBB144711EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3565D4B7-8137-4F99-A771-18C96DAA27BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29385" yWindow="3225" windowWidth="20370" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -584,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>21</v>

--- a/JsonConverter/ExcelFiles/WJUnit.xlsx
+++ b/JsonConverter/ExcelFiles/WJUnit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\WJMainProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3565D4B7-8137-4F99-A771-18C96DAA27BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1698297-6521-43F2-8386-557F07FB0935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29385" yWindow="3225" windowWidth="20370" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34635" yWindow="3780" windowWidth="22485" windowHeight="11145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WJTable_Unit" sheetId="1" r:id="rId1"/>
@@ -718,7 +718,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="5">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>20</v>
